--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647311</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135647314</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135647315</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647327</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135647322</v>
       </c>
       <c r="B6" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135647323</v>
       </c>
       <c r="B7" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647311</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135647314</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135647315</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647327</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135647322</v>
       </c>
       <c r="B6" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135647323</v>
       </c>
       <c r="B7" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135647313</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135647321</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647311</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135647314</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135647315</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647327</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135647322</v>
       </c>
       <c r="B6" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135647323</v>
       </c>
       <c r="B7" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647311</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135647314</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135647315</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647327</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135647322</v>
       </c>
       <c r="B6" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135647323</v>
       </c>
       <c r="B7" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135647313</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135647321</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28423-2026 artfynd.xlsx
+++ b/artfynd/A 28423-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647311</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135647314</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135647315</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647327</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135647322</v>
       </c>
       <c r="B6" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135647323</v>
       </c>
       <c r="B7" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135647313</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135647321</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135647328</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>135647329</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>135647330</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
